--- a/data/trans_camb/P6905-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 16,7</t>
+          <t>-17,03; 18,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 27,31</t>
+          <t>-12,09; 26,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 21,2</t>
+          <t>-17,88; 21,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 27,96</t>
+          <t>-13,03; 30,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 13,54</t>
+          <t>-26,65; 12,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 24,08</t>
+          <t>-13,75; 21,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 16,89</t>
+          <t>-9,91; 16,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 14,89</t>
+          <t>-12,94; 14,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 16,36</t>
+          <t>-8,23; 16,72</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,18; 63,04</t>
+          <t>-41,93; 73,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 105,13</t>
+          <t>-32,1; 93,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 83,12</t>
+          <t>-42,9; 83,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 115,21</t>
+          <t>-27,85; 113,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 53,22</t>
+          <t>-58,24; 47,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 91,59</t>
+          <t>-28,81; 81,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 62,3</t>
+          <t>-23,77; 57,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 51,48</t>
+          <t>-32,02; 50,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 56,98</t>
+          <t>-19,63; 56,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 24,23</t>
+          <t>-20,04; 25,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 32,34</t>
+          <t>-15,52; 31,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 17,08</t>
+          <t>-21,7; 19,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 17,21</t>
+          <t>-31,51; 17,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,0; -5,56</t>
+          <t>-50,13; -4,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,75; -13,19</t>
+          <t>-50,65; -13,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 15,15</t>
+          <t>-20,32; 11,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 7,5</t>
+          <t>-25,97; 6,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-30,19; -2,08</t>
+          <t>-32,41; -3,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,15; 149,03</t>
+          <t>-51,93; 174,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 198,95</t>
+          <t>-46,92; 199,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 118,46</t>
+          <t>-58,54; 139,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 29,14</t>
+          <t>-43,46; 28,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,29; -9,17</t>
+          <t>-67,02; -8,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,74; -23,24</t>
+          <t>-66,39; -21,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 41,33</t>
+          <t>-38,27; 27,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 18,75</t>
+          <t>-48,7; 16,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,35; -2,81</t>
+          <t>-58,54; -8,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -3,12</t>
+          <t>-31,09; -1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,99; -6,35</t>
+          <t>-34,37; -4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,31; -2,56</t>
+          <t>-33,67; -2,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 24,01</t>
+          <t>-33,8; 28,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 54,66</t>
+          <t>-29,45; 54,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 18,59</t>
+          <t>-42,88; 22,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 1,53</t>
+          <t>-26,84; -0,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -2,4</t>
+          <t>-28,46; -1,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -3,1</t>
+          <t>-31,05; -2,98</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,86; -9,06</t>
+          <t>-64,19; -3,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,63; -17,15</t>
+          <t>-72,1; -10,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,22; -4,4</t>
+          <t>-72,84; -5,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 125,79</t>
+          <t>-56,78; 158,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 233,24</t>
+          <t>-54,16; 255,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,34; 85,51</t>
+          <t>-71,86; 121,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 4,88</t>
+          <t>-55,48; -1,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,94; -4,42</t>
+          <t>-60,41; -4,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,02; -6,78</t>
+          <t>-65,31; -7,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 4,91</t>
+          <t>-15,03; 5,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 6,85</t>
+          <t>-13,01; 7,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 2,95</t>
+          <t>-18,85; 4,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 1,64</t>
+          <t>-34,18; 1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 15,59</t>
+          <t>-20,44; 14,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -0,67</t>
+          <t>-30,91; -0,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 2,6</t>
+          <t>-15,1; 2,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 8,74</t>
+          <t>-8,53; 9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 3,22</t>
+          <t>-14,74; 2,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 20,48</t>
+          <t>-49,38; 24,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 30,35</t>
+          <t>-41,8; 36,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 12,14</t>
+          <t>-60,87; 18,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 4,32</t>
+          <t>-60,32; 5,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 41,63</t>
+          <t>-34,83; 38,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,21; -1,85</t>
+          <t>-52,6; -0,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 8,15</t>
+          <t>-42,33; 11,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 31,78</t>
+          <t>-23,43; 34,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 11,87</t>
+          <t>-41,27; 10,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 27,59</t>
+          <t>-8,03; 27,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 23,19</t>
+          <t>-6,03; 24,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 13,87</t>
+          <t>-14,73; 15,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 36,17</t>
+          <t>0,25; 35,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 40,06</t>
+          <t>5,7; 41,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 22,17</t>
+          <t>-13,13; 23,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 27,78</t>
+          <t>0,21; 26,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 26,18</t>
+          <t>1,29; 25,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 17,23</t>
+          <t>-8,93; 16,94</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 212,47</t>
+          <t>-33,03; 213,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 204,64</t>
+          <t>-26,38; 199,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 129,51</t>
+          <t>-57,68; 150,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 251,86</t>
+          <t>-2,34; 264,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,83; 302,85</t>
+          <t>17,64; 347,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 142,11</t>
+          <t>-44,38; 164,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,17; 182,35</t>
+          <t>-1,97; 166,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,85; 177,77</t>
+          <t>4,07; 176,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 110,24</t>
+          <t>-37,55; 113,2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4,06</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,64</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,85; 2,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,14; 4,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,78; -0,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,5; 9,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,64; 9,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,46; 0,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,75; 3,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,1; 4,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,32; -0,3</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-13,5%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-9,59%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-23,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-21,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,71%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-17,44%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,45; 10,02</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-28,7; 15,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-41,48; -0,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,26; 25,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,72; 26,01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-44,11; -0,45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,98; 11,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,91; 15,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-34,16; -1,57</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-2,88</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-7,2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-8,64</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-5,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-10,58; 2,25</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-9,03; 3,71</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-13,92; -0,03</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-8,84; 10,02</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 9,98</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-19,45; -0,24</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-6,71; 4,73</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-6,86; 3,86</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-11,48; -0,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>-13,5%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-9,59%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-23,97%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-21,09%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-4,66%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-2,71%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-17,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-32,03; 9,38</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-27,52; 13,67</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-42,66; 0,23</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-19,12; 27,22</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-19,22; 27,17</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-43,67; -0,87</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-18,97; 15,97</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-19,16; 12,36</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-31,94; -1,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6905-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>6,39</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 18,55</t>
+          <t>-17,97; 16,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 26,21</t>
+          <t>-11,33; 26,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 21,39</t>
+          <t>-11,04; 26,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 30,0</t>
+          <t>-14,1; 28,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 12,7</t>
+          <t>-25,46; 13,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 21,89</t>
+          <t>-15,76; 20,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 16,91</t>
+          <t>-9,63; 16,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 14,6</t>
+          <t>-14,02; 14,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 16,72</t>
+          <t>-6,57; 19,59</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 73,52</t>
+          <t>-41,86; 66,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 93,25</t>
+          <t>-28,68; 105,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 83,83</t>
+          <t>-28,2; 107,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 113,56</t>
+          <t>-29,8; 111,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 47,75</t>
+          <t>-55,21; 62,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 81,43</t>
+          <t>-33,94; 84,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 57,45</t>
+          <t>-22,79; 57,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 50,55</t>
+          <t>-33,44; 49,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 56,83</t>
+          <t>-15,26; 67,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-32,81</t>
+          <t>-32,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-17,46</t>
+          <t>-17,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 25,01</t>
+          <t>-18,02; 24,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 31,35</t>
+          <t>-15,02; 30,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 19,24</t>
+          <t>-19,99; 17,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 17,93</t>
+          <t>-31,45; 18,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,13; -4,89</t>
+          <t>-51,24; -4,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,65; -13,51</t>
+          <t>-49,36; -10,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 11,55</t>
+          <t>-22,3; 13,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 6,64</t>
+          <t>-24,83; 8,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-32,41; -3,26</t>
+          <t>-32,04; -2,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,49%</t>
+          <t>-6,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-47,59%</t>
+          <t>-46,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-36,76%</t>
+          <t>-36,21%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 174,99</t>
+          <t>-50,95; 148,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 199,37</t>
+          <t>-44,27; 196,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 139,82</t>
+          <t>-58,95; 125,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 28,69</t>
+          <t>-41,24; 30,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,02; -8,67</t>
+          <t>-66,35; -7,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,39; -21,21</t>
+          <t>-64,96; -19,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 27,89</t>
+          <t>-38,69; 35,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 16,33</t>
+          <t>-46,83; 22,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,54; -8,22</t>
+          <t>-58,4; -4,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,48</t>
+          <t>-16,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,81</t>
+          <t>-12,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-17,75</t>
+          <t>-15,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,09; -1,92</t>
+          <t>-31,85; -2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-34,37; -4,08</t>
+          <t>-33,48; -5,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,67; -2,64</t>
+          <t>-30,18; 3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 28,44</t>
+          <t>-38,19; 25,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 54,16</t>
+          <t>-26,76; 54,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 22,56</t>
+          <t>-42,46; 16,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,84; -0,48</t>
+          <t>-26,24; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,46; -1,65</t>
+          <t>-28,61; -0,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,05; -2,98</t>
+          <t>-29,79; 0,53</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-46,97%</t>
+          <t>-39,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-29,62%</t>
+          <t>-28,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,56%</t>
+          <t>-36,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,19; -3,55</t>
+          <t>-65,78; -6,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,1; -10,2</t>
+          <t>-69,39; -12,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -5,39</t>
+          <t>-67,53; 11,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,78; 158,33</t>
+          <t>-60,83; 121,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 255,49</t>
+          <t>-52,33; 233,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 121,99</t>
+          <t>-68,28; 93,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,48; -1,55</t>
+          <t>-54,25; 3,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -4,19</t>
+          <t>-60,33; 0,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,31; -7,35</t>
+          <t>-61,83; 4,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-16,23</t>
+          <t>-16,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-4,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 5,07</t>
+          <t>-15,98; 4,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 7,96</t>
+          <t>-13,66; 6,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 4,22</t>
+          <t>-13,38; 8,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 1,73</t>
+          <t>-32,92; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 14,28</t>
+          <t>-21,61; 13,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,91; -0,24</t>
+          <t>-31,77; -1,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 2,56</t>
+          <t>-14,64; 3,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 9,17</t>
+          <t>-7,98; 9,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 2,28</t>
+          <t>-12,58; 4,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-27,87%</t>
+          <t>-13,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,77%</t>
+          <t>-34,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,15%</t>
+          <t>-14,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 24,69</t>
+          <t>-51,07; 23,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 36,67</t>
+          <t>-42,69; 32,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 18,68</t>
+          <t>-44,85; 36,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 5,04</t>
+          <t>-57,69; 5,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 38,68</t>
+          <t>-37,15; 36,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,6; -0,79</t>
+          <t>-53,56; -3,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 11,52</t>
+          <t>-42,17; 11,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 34,54</t>
+          <t>-23,43; 35,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 10,11</t>
+          <t>-35,86; 15,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>10,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>5,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 27,18</t>
+          <t>-9,0; 27,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 24,41</t>
+          <t>-7,24; 22,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 15,81</t>
+          <t>-17,01; 10,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 35,84</t>
+          <t>0,31; 37,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 41,68</t>
+          <t>4,84; 40,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 23,0</t>
+          <t>-3,01; 23,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 26,17</t>
+          <t>2,22; 28,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 25,93</t>
+          <t>2,45; 25,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 16,94</t>
+          <t>-3,48; 15,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,22%</t>
+          <t>-18,1%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 213,61</t>
+          <t>-38,73; 222,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 199,05</t>
+          <t>-28,0; 182,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 150,85</t>
+          <t>-63,38; 90,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 264,57</t>
+          <t>-8,45; 270,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,64; 347,25</t>
+          <t>15,98; 291,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 164,96</t>
+          <t>-12,35; 179,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 166,21</t>
+          <t>5,31; 189,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,07; 176,1</t>
+          <t>10,52; 183,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,55; 113,2</t>
+          <t>-14,74; 96,27</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-7,2</t>
+          <t>-4,81</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-8,64</t>
+          <t>-7,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-4,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 2,63</t>
+          <t>-10,93; 2,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,05</t>
+          <t>-9,49; 3,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -0,2</t>
+          <t>-11,83; 2,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 9,37</t>
+          <t>-10,16; 9,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 9,53</t>
+          <t>-7,8; 11,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 0,34</t>
+          <t>-15,26; 0,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,8</t>
+          <t>-7,24; 4,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,9</t>
+          <t>-6,47; 3,96</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -0,3</t>
+          <t>-9,37; 0,73</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-23,97%</t>
+          <t>-16,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,09%</t>
+          <t>-17,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>-12,94%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 10,02</t>
+          <t>-33,63; 8,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 15,23</t>
+          <t>-28,6; 12,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -0,59</t>
+          <t>-35,7; 7,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 25,63</t>
+          <t>-22,32; 26,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 26,01</t>
+          <t>-17,72; 32,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -0,45</t>
+          <t>-33,27; 2,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 11,39</t>
+          <t>-19,6; 14,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 15,67</t>
+          <t>-18,03; 12,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,16; -1,57</t>
+          <t>-26,29; 2,35</t>
         </is>
       </c>
     </row>
